--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/03_Negotiation_Risk_Matrix.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/03_Negotiation_Risk_Matrix.xlsx
@@ -578,6 +578,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>

--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/03_Negotiation_Risk_Matrix.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/03_Negotiation_Risk_Matrix.xlsx
@@ -581,7 +581,7 @@
     <row r="3">
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Fair, benchmarked, documented consideration to Tribe; public-purpose protections; reversion; arm's-length terms.</t>
+          <t>Fair, benchmarked, documented consideration to Lumbee Tribe; public-purpose protections; reversion; arm's-length terms.</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Clear default/cure; Tribe emergency step-in; replacement-operator plan; escrow of records/credentials.</t>
+          <t>Clear default/cure; Lumbee Tribe emergency step-in; replacement-operator plan; escrow of records/credentials.</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
